--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>173495.42</v>
+        <v>171588.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1314-62-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20487.16</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>32041.65</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>1605-404-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>743345.55</v>
+        <v>154680.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1605-404-CM25</t>
+          <t>1111089-522-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>153592.25</v>
+        <v>339530.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>519302-164-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>65.999.669-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>340882.62</v>
+        <v>20674.73</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>531687.75</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>31709.63</v>
+        <v>31938.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>937232-1121-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>625125.4</v>
+        <v>501384.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057539-29772-CM25</t>
+          <t>1177296-473-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,37 +1082,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39684.17</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>1057539-29772-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,37 +1143,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>68367.22</v>
+        <v>40045.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>3232-795-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,57 +1204,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>895721.87</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>609-569-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1264,12 +1260,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1279,12 +1275,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1309,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>49488.86</v>
+        <v>68833.08</v>
       </c>
     </row>
     <row r="15">
@@ -1370,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>295182.2</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,12 +1397,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1431,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>654773.7</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>612-49-SE26</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,27 +1443,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,32 +1473,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>425249.38</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45-527-CM25</t>
+          <t>612-49-SE26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1517,22 +1509,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,28 +1534,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>253458.04</v>
+        <v>421786.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>45-527-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,7 +1574,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,27 +1584,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.771.610-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1618,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>427192.07</v>
+        <v>254565.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>711841-49-SE26</t>
+          <t>3756-897-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1639,7 +1635,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1649,47 +1645,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>222685.76</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>711841-49-SE26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1709,48 +1701,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>40568.04</v>
+        <v>224012.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1765,37 +1761,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1805,13 +1801,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48857.96</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>1725-83-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1826,7 +1822,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1836,47 +1832,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7941.53</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>609-31-SE26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1896,48 +1888,52 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45818.31</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5153-348-CM26</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1952,7 +1948,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1962,27 +1958,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1992,13 +1988,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>76218.81</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5153-349-CM26</t>
+          <t>5153-348-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2053,13 +2049,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>77492.14</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1704-1310-CM26</t>
+          <t>5153-349-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2069,42 +2065,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2114,13 +2110,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>73550.39999999999</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>874750-67-CM26</t>
+          <t>1057501-2182-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2130,12 +2126,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2145,27 +2141,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2175,13 +2171,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>124323.82</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>1704-1310-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2196,12 +2192,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2221,12 +2217,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2236,13 +2232,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>46458.46</v>
+        <v>73712.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>874750-67-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2257,7 +2253,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2267,27 +2263,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2297,13 +2293,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15706.87</v>
+        <v>123466.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>812261-9882-CM25</t>
+          <t>1704-1373-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2318,7 +2314,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2328,27 +2324,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.866.212-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2358,13 +2354,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1722655.54</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1973-722-CM26</t>
+          <t>5416-143-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2379,37 +2375,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2419,13 +2415,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19907.64</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>812261-9882-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2435,42 +2431,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.866.212-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2480,13 +2476,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>766143.0699999999</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1743-66-CM26</t>
+          <t>1973-722-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2496,12 +2492,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2511,27 +2507,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2541,13 +2537,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>417442.81</v>
+        <v>19825.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,37 +2558,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2602,13 +2598,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>386079.54</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>1743-66-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2623,37 +2619,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>676558.0699999999</v>
+        <v>405227.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>1057539-2804-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2679,12 +2675,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2694,27 +2690,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2724,13 +2720,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46450.67</v>
+        <v>388618.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2740,12 +2736,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2755,27 +2751,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2785,13 +2781,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46450.67</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1415862-28-SE26</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2806,57 +2802,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>360947.33</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2871,7 +2863,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2881,47 +2873,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1641207.55</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>1415862-28-SE26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2936,7 +2924,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2946,12 +2934,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2961,28 +2949,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>313385.18</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>599-82-CM26</t>
+          <t>591-155-SE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2997,22 +2989,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3022,28 +3014,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>70936.44</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3058,7 +3054,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3068,12 +3064,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3083,12 +3079,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3098,13 +3094,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>108751.26</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3598-440-CM26</t>
+          <t>599-58-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3114,42 +3110,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3159,13 +3155,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>253601.02</v>
+        <v>109632.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>3598-440-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3180,37 +3176,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3220,13 +3216,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>89270.78</v>
+        <v>257242.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>538598-2171-CM26</t>
+          <t>621923-26-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3241,22 +3237,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3266,12 +3262,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3281,13 +3277,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>417776.85</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>538598-2171-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3297,12 +3293,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3312,12 +3308,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3327,12 +3323,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3342,7 +3338,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1690339.34</v>
+        <v>412618.31</v>
       </c>
     </row>
     <row r="48">
@@ -3403,13 +3399,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>450579.75</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>894244-4-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3424,7 +3420,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3434,12 +3430,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3449,12 +3445,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3464,13 +3460,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>481036.15</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3485,7 +3481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3495,12 +3491,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3510,12 +3506,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3525,13 +3521,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>914845.87</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>869591-35-CM26</t>
+          <t>591-90-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3546,7 +3542,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3556,12 +3552,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3571,12 +3567,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3586,13 +3582,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>50854.08</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>869591-35-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3617,27 +3613,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3647,13 +3643,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>15789.24</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>711841-243-SE26</t>
+          <t>765-158-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3668,7 +3664,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3678,102 +3674,712 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17460.36</v>
+        <v>15606.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>711841-243-SE26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>60.103.000-4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ANTICIPA S A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>17375.86</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>606-299-CM26</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>60.513.000-3</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Pragma Informatica S.A.</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>134762.36</v>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>135674.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>711841-228-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.103.000-4</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>18470.68</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1016-73-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>30606.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>606-311-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.513.000-3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>85311.75</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>622-302-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.805.000-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>24372.73</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2345-267-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>330201.73</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3954-31-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.091.500-6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>223123.85</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1005498-124-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>60231.56</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4168-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>36252.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>918434-450-CM25</t>
+          <t>3756-429-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>171588.93</v>
+        <v>313544.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>731-19-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,27 +600,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>32268.6</v>
+        <v>196230.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>1778-586-CM24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>748610.75</v>
+        <v>31119.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1605-404-CM25</t>
+          <t>2677-28-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>154680.16</v>
+        <v>60481.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>1233616-16-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,42 +768,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Ñuble</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>339530.09</v>
+        <v>13532.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>519302-164-CM25</t>
+          <t>5416-100-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.999.669-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20674.73</v>
+        <v>12419.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>2268-363-CM24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,42 +890,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>611852.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3756-813-SE25</t>
+          <t>1186229-14-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,62 +951,58 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>31938.36</v>
+        <v>1114399.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>937232-1121-CM25</t>
+          <t>1725-4419-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>501384.71</v>
+        <v>56941.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>1704-134-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,17 +1088,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>626037.92</v>
+        <v>40838.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057539-29772-CM25</t>
+          <t>1216094-10-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,42 +1134,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40045.88</v>
+        <v>41405.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3232-795-CM25</t>
+          <t>1314-28-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,42 +1195,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>35024.99</v>
+        <v>19130.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>3598-171-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,42 +1256,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>68833.08</v>
+        <v>205644.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>545774-17-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,42 +1317,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>291592.37</v>
+        <v>30501.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>5574-19-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,27 +1393,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>48887.01</v>
+        <v>22003.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>731-48-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>664434.1899999999</v>
+        <v>69941.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>612-49-SE26</t>
+          <t>1016414-35-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,62 +1500,58 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>421786.91</v>
+        <v>69873.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45-527-CM25</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1569,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,27 +1576,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1614,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>254565.52</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1630,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1645,27 +1637,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1675,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>430686.32</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>711841-49-SE26</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1691,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1706,47 +1698,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>224012.71</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>1876-52-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,42 +1744,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>40809.78</v>
+        <v>514712.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>1093219-4-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1817,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1862,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>48811.95</v>
+        <v>39262.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>2153-243-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1878,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1893,47 +1881,43 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7902.37</v>
+        <v>606765.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1943,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1958,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1988,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>45592.37</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5153-348-CM26</t>
+          <t>3598-430-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2004,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2019,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2049,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>75841.3</v>
+        <v>23779.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5153-349-CM26</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2065,42 +2049,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2110,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>77108.33</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057501-2182-CM26</t>
+          <t>2279-370-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2126,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2141,17 +2125,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2171,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16288.11</v>
+        <v>63214.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704-1310-CM26</t>
+          <t>1314-3-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2187,42 +2171,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2232,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>73712.03</v>
+        <v>51260.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>874750-67-CM26</t>
+          <t>1704-2933-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2248,42 +2232,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2293,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>123466.9</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>1704-2935-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2309,17 +2293,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2334,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2354,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>47308.62</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>1111089-267-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2370,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2385,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2415,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15723.01</v>
+        <v>55054.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>812261-9882-CM25</t>
+          <t>730566-248-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,42 +2415,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.866.212-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2476,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1703050.45</v>
+        <v>44731.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1973-722-CM26</t>
+          <t>609-153-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2492,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2507,27 +2491,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2537,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19825.16</v>
+        <v>24119.18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2553,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2568,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2598,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>750328.3100000001</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1743-66-CM26</t>
+          <t>711841-358-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2614,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2629,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2659,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>405227.73</v>
+        <v>19888.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>557639-793-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2675,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2690,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2720,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>388618.51</v>
+        <v>1108739.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>1725-5144-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2736,42 +2720,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2781,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>681911.34</v>
+        <v>20039.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2797,42 +2781,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2842,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>46529.02</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1743-384-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2858,42 +2842,42 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2903,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>46529.02</v>
+        <v>175880.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1415862-28-SE26</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2919,62 +2903,58 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>357020.86</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>2766-844-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2984,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2999,47 +2979,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1643132.54</v>
+        <v>11457.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>652-204-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3049,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3064,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3094,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>316206.29</v>
+        <v>1637401.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>548874-229-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3110,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3125,17 +3101,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3155,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>109632.69</v>
+        <v>14153.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3598-440-CM26</t>
+          <t>711841-515-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3171,42 +3147,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3216,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>257242.59</v>
+        <v>23542.74</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>1005498-216-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3232,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3247,27 +3223,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3277,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>91015.17999999999</v>
+        <v>25350.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>538598-2171-CM26</t>
+          <t>1725-5365-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3293,42 +3269,42 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3338,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>412618.31</v>
+        <v>25949.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>709603-152-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3354,42 +3330,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3399,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>452162.74</v>
+        <v>54154.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>765-349-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3415,42 +3391,42 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3460,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1696277.88</v>
+        <v>10590.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>606-368-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3476,42 +3452,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3521,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>482098.69</v>
+        <v>128858.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>711841-549-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3537,42 +3513,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3582,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>913082.5600000001</v>
+        <v>16686.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>869591-35-CM26</t>
+          <t>4127-196-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3598,42 +3574,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3643,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>50266.24</v>
+        <v>510212.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>557639-1899-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3659,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3674,27 +3650,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3704,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>15606.73</v>
+        <v>56223.46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>711841-243-SE26</t>
+          <t>45-349-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3720,62 +3696,58 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17375.86</v>
+        <v>41671.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>606-299-CM26</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3785,42 +3757,42 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3830,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>135674.88</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>711841-600-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3846,42 +3818,42 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3891,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1718926.68</v>
+        <v>30902.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>711841-228-CM26</t>
+          <t>2380-2242-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3907,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3922,27 +3894,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Atacama </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3952,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>18470.68</v>
+        <v>30283.05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1016-73-CM26</t>
+          <t>2766-1078-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3968,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3998,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4013,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>30606.2</v>
+        <v>7722.32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>606-311-CM26</t>
+          <t>603663-378-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4029,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4074,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>85311.75</v>
+        <v>8783.790000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>622-302-CM26</t>
+          <t>1067455-173-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4090,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4105,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4120,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4135,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>24372.73</v>
+        <v>66369.78999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2345-267-CM26</t>
+          <t>584105-313-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4151,27 +4123,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4196,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>330201.73</v>
+        <v>382106.17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3954-31-CM26</t>
+          <t>609-481-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4212,42 +4184,42 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4257,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>223123.85</v>
+        <v>31269.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1005498-124-CM26</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4273,32 +4245,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4318,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>60231.56</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4168-1247-CM26</t>
+          <t>1605-367-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4334,42 +4306,42 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4379,6 +4351,3938 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
+        <v>444468.14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>918434-450-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.980.680-8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>171588.93</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1314-62-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60.706.000-2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>20378.11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2580-1226-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Superintendencia de Pensiones</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>748610.75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1605-404-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>60.803.000-K</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>154680.16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>587-654-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.801.000-7</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>32268.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1111089-522-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>339530.09</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>519302-164-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>65.999.669-3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>20674.73</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>586-630-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>530945.6899999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2777-884-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.081.200-2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENGO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>154690.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3756-813-SE25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>31938.36</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2766-1316-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>69.072.000-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>7057.25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>876-352-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.101.000-3</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>68186.2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3944-345-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.091.500-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>50321.79</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1005498-305-SE25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>83686.95</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>937232-1121-CM25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.980.620-4</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>501384.71</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1177296-473-CM25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>626037.92</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>635-5072-CM25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>34583.87</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3232-795-CM25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>35024.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>591-7730-SE25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>901825.33</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>609-569-CM25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>68833.08</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>812261-7571-CM25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>291592.37</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>812261-7572-CM25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>48887.01</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2428-1-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>16696.03</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1233616-170-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>15074.98</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>635-84-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>22477.75</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>612-49-SE26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>421786.91</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2366-64-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>34277.51</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3756-897-CM25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>430686.32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2677-36-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.080.500-6</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>RAYEN SALUD SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>63261.21</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>711841-49-SE26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>60.103.000-4</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>224012.71</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1725-83-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>48811.95</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>609-31-SE26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>7902.37</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1704-1105-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>45592.37</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1057501-2182-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>16288.11</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1035206-191-CM25</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>65.165.411-4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>185339.03</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1704-1373-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>47308.62</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5416-143-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>15723.01</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1743-66-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.091.100-0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>405227.73</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>545774-18-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.070.800-0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>39248.25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1704-2534-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>46529.02</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1704-2535-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>46529.02</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2766-212-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>69.072.000-0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>7350.17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1415862-28-SE26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Instituto de Seguridad Laboral</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>357020.86</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1177296-550-CM25</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>316206.29</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>599-82-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>71491.19</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2766-277-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>69.072.000-0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>14001.95</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5574-43-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>57074.88</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>599-58-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>109632.69</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>3598-440-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.091.300-3</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>257242.59</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>621923-26-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>53.314.945-6</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>91015.17999999999</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4134-401-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>452162.74</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>894244-4-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1696277.88</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>5586-761-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>133390.47</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>812261-62-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>482098.69</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>591-90-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>913082.5600000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>765-158-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>15606.73</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2455-107-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>69.071.000-5</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>260658.45</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>711841-228-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>60.103.000-4</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>18470.68</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1016-73-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>30606.2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2345-267-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>330201.73</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3954-31-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>69.091.500-6</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>223123.85</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1005498-124-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>60231.56</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4168-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
         <v>36252.2</v>
       </c>
     </row>

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desarrollo-y-man top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="desarrollo-y-man top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3756-429-CM24</t>
+          <t>731-19-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>313544.04</v>
+        <v>196230.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>731-19-CM25</t>
+          <t>1778-586-CM24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>196230.22</v>
+        <v>31119.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1778-586-CM24</t>
+          <t>2677-28-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -656,32 +656,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>31119.04</v>
+        <v>60481.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2677-28-CM25</t>
+          <t>1233616-16-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,32 +717,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>60481.06</v>
+        <v>13532.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1233616-16-CM25</t>
+          <t>5416-100-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,27 +783,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13532.73</v>
+        <v>12419.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5416-100-CM25</t>
+          <t>2268-363-CM24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,37 +834,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12419.93</v>
+        <v>611852.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2268-363-CM24</t>
+          <t>1186229-14-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>611852.64</v>
+        <v>1114399.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1186229-14-CM25</t>
+          <t>1725-4419-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,27 +966,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1114399.84</v>
+        <v>56941.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1725-4419-CM25</t>
+          <t>1704-134-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56941.6</v>
+        <v>40838.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1704-134-CM25</t>
+          <t>1216094-10-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>40838.18</v>
+        <v>41405.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1216094-10-CM25</t>
+          <t>1314-28-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>41405.99</v>
+        <v>19130.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1314-28-CM25</t>
+          <t>545774-17-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19130.7</v>
+        <v>30501.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3598-171-CM25</t>
+          <t>5574-19-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,37 +1261,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>205644.03</v>
+        <v>22003.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>545774-17-CM25</t>
+          <t>1057414-113-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,42 +1317,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30501.57</v>
+        <v>251095.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5574-19-CM25</t>
+          <t>731-48-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>22003.04</v>
+        <v>69941.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>731-48-CM25</t>
+          <t>1016414-35-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>69941.44</v>
+        <v>69873.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1016414-35-CM25</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>69873.17</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="19">
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>138546.34</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1607-86-CM25</t>
+          <t>1876-52-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>629930.14</v>
+        <v>514712.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1876-52-CM25</t>
+          <t>1093219-4-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>514712.49</v>
+        <v>39262.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1093219-4-CM25</t>
+          <t>2153-243-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>39262.17</v>
+        <v>606765.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2153-243-CM25</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,27 +1871,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.608.503-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hospital Sanatorio San José de Maipo</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>606765.79</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2307-2925-CM25</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,37 +1932,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>167401.82</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3598-430-CM25</t>
+          <t>2279-370-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23779.96</v>
+        <v>63214.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1607-93-CM25</t>
+          <t>1057414-203-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>705074.45</v>
+        <v>18269.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2279-370-CM25</t>
+          <t>1314-3-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>63214.01</v>
+        <v>51260.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1314-3-CM25</t>
+          <t>1704-2933-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,32 +2181,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>51260.51</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704-2933-CM25</t>
+          <t>1704-2935-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1704-2935-CM25</t>
+          <t>1111089-267-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,42 +2293,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>40467.49</v>
+        <v>55054.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1111089-267-CM25</t>
+          <t>730566-248-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>55054.96</v>
+        <v>44731.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>730566-248-CM25</t>
+          <t>609-153-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>44731.6</v>
+        <v>24119.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>609-153-CM25</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24119.18</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>587-167-CM25</t>
+          <t>711841-358-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>834321.6800000001</v>
+        <v>19888.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>711841-358-CM25</t>
+          <t>557639-793-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,42 +2598,42 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19888.14</v>
+        <v>1108739.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>557639-793-CM25</t>
+          <t>1725-5144-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,37 +2664,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1108739.21</v>
+        <v>20039.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1725-5144-CM25</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20039.98</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>761-328-CM25</t>
+          <t>2766-844-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1601122.18</v>
+        <v>11457.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1743-384-CM25</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>175880.58</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>591-7471-CM25</t>
+          <t>652-204-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2908,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1564746.61</v>
+        <v>1637401.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2766-844-CM25</t>
+          <t>548874-229-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11457.42</v>
+        <v>14153.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>652-204-CM25</t>
+          <t>1005498-216-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1637401.65</v>
+        <v>25350.68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>548874-229-CM25</t>
+          <t>711841-515-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14153.37</v>
+        <v>23542.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>711841-515-CM25</t>
+          <t>1725-5365-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>23542.74</v>
+        <v>25949.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1005498-216-CM25</t>
+          <t>709603-152-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>25350.68</v>
+        <v>54154.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1725-5365-CM25</t>
+          <t>765-349-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25949.03</v>
+        <v>10590.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>709603-152-CM25</t>
+          <t>606-368-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.980.220-9</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>54154.4</v>
+        <v>128858.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>765-349-CM25</t>
+          <t>711841-549-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10590.65</v>
+        <v>16686.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>606-368-CM25</t>
+          <t>1398-2284-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,37 +3457,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>128858.47</v>
+        <v>36105.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>711841-549-CM25</t>
+          <t>4127-196-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>16686.91</v>
+        <v>510212.77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4127-196-CM25</t>
+          <t>557639-1899-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,42 +3574,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>510212.77</v>
+        <v>56223.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>557639-1899-CM25</t>
+          <t>5153-2175-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3650,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>56223.46</v>
+        <v>28380.12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>45-349-CM25</t>
+          <t>5153-2195-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41671.09</v>
+        <v>68639.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>761-628-CM25</t>
+          <t>45-349-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>40057.03</v>
+        <v>41671.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>711841-600-CM25</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>30902.16</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2380-2242-CM25</t>
+          <t>711841-600-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,37 +3884,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>30283.05</v>
+        <v>30902.16</v>
       </c>
     </row>
     <row r="58">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>603663-378-CM25</t>
+          <t>2380-2242-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,37 +4006,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8783.790000000001</v>
+        <v>30283.05</v>
       </c>
     </row>
     <row r="60">
@@ -4113,7 +4113,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>584105-313-CM25</t>
+          <t>603663-378-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>382106.17</v>
+        <v>8783.790000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>609-481-CM25</t>
+          <t>584105-313-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>31269.18</v>
+        <v>382106.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>765-409-CM25</t>
+          <t>609-481-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>37572.09</v>
+        <v>31269.18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1605-367-CM25</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,27 +4321,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>444468.14</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>918434-450-CM25</t>
+          <t>1605-367-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>171588.93</v>
+        <v>444468.14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1314-62-CM25</t>
+          <t>918434-450-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>20378.11</v>
+        <v>171588.93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>1314-62-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,22 +4494,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>748610.75</v>
+        <v>20378.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1605-404-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>154680.16</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>32268.6</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>1605-404-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>339530.09</v>
+        <v>154680.16</v>
       </c>
     </row>
     <row r="71">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>1111089-522-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,27 +4799,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>339530.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2777-884-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,37 +4860,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>154690.6</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3756-813-SE25</t>
+          <t>2777-884-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,41 +4931,37 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>31938.36</v>
+        <v>154690.6</v>
       </c>
     </row>
     <row r="75">
@@ -5113,7 +5109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5133,7 +5129,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5174,7 +5170,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5249,7 +5245,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5310,7 +5306,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5381,7 +5377,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5741,7 +5737,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5802,7 +5798,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5833,7 +5829,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>635-84-CM26</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5848,7 +5844,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5858,27 +5854,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5888,13 +5884,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>22477.75</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>612-49-SE26</t>
+          <t>635-84-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5904,62 +5900,58 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>421786.91</v>
+        <v>22477.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2366-64-CM26</t>
+          <t>612-49-SE26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5974,53 +5966,57 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>34277.51</v>
+        <v>421786.91</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>2366-64-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6035,7 +6031,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6045,27 +6041,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6075,7 +6071,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>430686.32</v>
+        <v>34277.51</v>
       </c>
     </row>
     <row r="93">
@@ -6121,7 +6117,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6207,7 +6203,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6222,37 +6218,37 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6262,13 +6258,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>48811.95</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>1725-83-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6283,7 +6279,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6293,47 +6289,43 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7902.37</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>609-31-SE26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6353,48 +6345,52 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>45592.37</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057501-2182-CM26</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6409,7 +6405,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6419,27 +6415,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6449,13 +6445,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16288.11</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1035206-191-CM25</t>
+          <t>5153-348-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6465,12 +6461,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6480,27 +6476,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6510,13 +6506,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>185339.03</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>5153-349-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6526,12 +6522,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6541,27 +6537,27 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6571,13 +6567,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>47308.62</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>1057501-2182-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6587,12 +6583,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6602,27 +6598,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6632,13 +6628,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>15723.01</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1743-66-CM26</t>
+          <t>1035206-191-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6648,42 +6644,42 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6693,13 +6689,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>405227.73</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>545774-18-CM26</t>
+          <t>1704-1373-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6709,12 +6705,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6724,27 +6720,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6754,13 +6750,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>39248.25</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>5416-143-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6770,12 +6766,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6785,27 +6781,27 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6815,13 +6811,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>46529.02</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6831,42 +6827,42 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6876,13 +6872,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>46529.02</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2766-212-CM26</t>
+          <t>545774-18-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6892,12 +6888,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6907,12 +6903,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6937,13 +6933,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7350.17</v>
+        <v>39248.25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1415862-28-SE26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6953,27 +6949,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6983,32 +6979,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>357020.86</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7023,27 +7015,27 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7063,13 +7055,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>316206.29</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>599-82-CM26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7084,37 +7076,37 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7124,13 +7116,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>71491.19</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2766-277-CM26</t>
+          <t>2766-212-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7145,7 +7137,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7185,13 +7177,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>14001.95</v>
+        <v>7350.17</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5574-43-CM26</t>
+          <t>1415862-28-SE26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7206,22 +7198,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7231,28 +7223,32 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>57074.88</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7267,7 +7263,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7277,12 +7273,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7292,12 +7288,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7307,13 +7303,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>109632.69</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3598-440-CM26</t>
+          <t>5574-43-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7323,12 +7319,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7338,27 +7334,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7368,13 +7364,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>257242.59</v>
+        <v>57074.88</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>599-82-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7384,12 +7380,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7399,12 +7395,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7414,12 +7410,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7429,13 +7425,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>91015.17999999999</v>
+        <v>71491.19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4134-401-CM26</t>
+          <t>2766-277-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7445,12 +7441,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7460,27 +7456,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7490,13 +7486,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>452162.74</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>599-58-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7506,27 +7502,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7536,12 +7532,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7551,13 +7547,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1696277.88</v>
+        <v>109632.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5586-761-CM26</t>
+          <t>621923-26-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7567,42 +7563,42 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7612,13 +7608,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>133390.47</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>894244-4-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7633,7 +7629,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7643,12 +7639,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7658,12 +7654,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7673,13 +7669,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>482098.69</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>5586-761-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7694,7 +7690,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7704,27 +7700,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7734,13 +7730,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>913082.5600000001</v>
+        <v>133390.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7755,7 +7751,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7765,27 +7761,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7795,13 +7791,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>15606.73</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2455-107-CM26</t>
+          <t>591-90-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7816,7 +7812,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7826,27 +7822,27 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7856,13 +7852,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>260658.45</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>869591-35-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7872,12 +7868,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7887,27 +7883,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7917,13 +7913,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1718926.68</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>711841-228-CM26</t>
+          <t>765-158-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7933,12 +7929,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7948,17 +7944,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7978,13 +7974,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>18470.68</v>
+        <v>15606.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1016-73-CM26</t>
+          <t>2455-107-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7994,12 +7990,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8009,12 +8005,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8024,12 +8020,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8039,13 +8035,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>30606.2</v>
+        <v>260658.45</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2345-267-CM26</t>
+          <t>606-299-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8055,12 +8051,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8070,12 +8066,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8085,12 +8081,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8100,13 +8096,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>330201.73</v>
+        <v>135674.88</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3954-31-CM26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8121,7 +8117,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8131,12 +8127,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8146,12 +8142,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8161,13 +8157,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>223123.85</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1005498-124-CM26</t>
+          <t>711841-228-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8182,7 +8178,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8192,12 +8188,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8222,13 +8218,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>60231.56</v>
+        <v>18470.68</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4168-1247-CM26</t>
+          <t>1016-73-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8243,7 +8239,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8253,27 +8249,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8283,7 +8279,617 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>36252.2</v>
+        <v>30606.2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>606-311-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>60.513.000-3</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>85311.75</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>622-302-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>60.805.000-0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>24372.73</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2345-267-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>330201.73</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1005498-124-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>60231.56</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1005498-132-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>24744.2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>870-209-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>60.718.000-8</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>COMISION NACIONAL DE RIEGO</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>177904.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4931-114-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>274977.66</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2766-572-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.072.000-0</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>8351.34</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>5153-1605-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>37202.6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>606-375-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>60.513.000-3</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>12951.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>76.516.485-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.093.443-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>77.430.680-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1307,7 +1331,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057414-113-CM25</t>
+          <t>709603-45-SE25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1346,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,43 +1356,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>251095.95</v>
+        <v>42876.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>731-48-CM25</t>
+          <t>1057414-113-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1411,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,43 +1421,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>69941.44</v>
+        <v>251095.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1016414-35-CM25</t>
+          <t>731-48-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1476,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1486,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1501,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1516,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>69873.17</v>
+        <v>69941.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>1016414-35-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1537,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1547,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1562,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>138546.34</v>
+        <v>69873.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>812261-1322-CM24</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1642,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>262605.26</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1607-86-CM25</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1663,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1673,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1688,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1703,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>629930.14</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1876-52-CM25</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1724,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1734,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1749,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>514712.49</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1093219-4-CM25</t>
+          <t>1876-52-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1784,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1799,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1814,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>39262.17</v>
+        <v>514712.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2153-243-CM25</t>
+          <t>709603-64-SE25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1854,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1864,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.503-4</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hospital Sanatorio San José de Maipo</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1879,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>606765.79</v>
+        <v>54155.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2307-2925-CM25</t>
+          <t>1093219-4-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,37 +1919,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1959,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>167401.82</v>
+        <v>39262.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1607-93-CM25</t>
+          <t>2153-243-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1980,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1990,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +2005,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2020,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>705074.45</v>
+        <v>606765.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2279-370-CM25</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2041,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2051,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2081,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>63214.01</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057414-203-CM25</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2102,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,43 +2112,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>18269.1</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1314-3-CM25</t>
+          <t>2279-370-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2167,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2177,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2192,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>51260.51</v>
+        <v>63214.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704-2933-CM25</t>
+          <t>1057414-203-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2232,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,43 +2242,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>40467.49</v>
+        <v>18269.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704-2935-CM25</t>
+          <t>1314-3-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,48 +2302,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>40467.49</v>
+        <v>51260.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1111089-267-CM25</t>
+          <t>1704-2933-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,42 +2357,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2402,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>55054.96</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>730566-248-CM25</t>
+          <t>1704-2935-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2418,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2433,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2463,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>44731.6</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>609-153-CM25</t>
+          <t>1111089-267-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2484,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2509,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2524,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>24119.18</v>
+        <v>55054.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>587-167-CM25</t>
+          <t>730566-248-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2545,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2555,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,20 +2578,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>834321.6800000001</v>
+        <v>44731.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>711841-358-CM25</t>
+          <t>609-153-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2610,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2620,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2575,20 +2643,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>19888.14</v>
+        <v>24119.18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>557639-793-CM25</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,58 +2670,62 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1108739.21</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1725-5144-CM25</t>
+          <t>711841-358-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2735,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2750,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>20039.98</v>
+        <v>19888.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>761-328-CM25</t>
+          <t>557639-793-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,37 +2805,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2845,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1601122.18</v>
+        <v>1108739.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2766-844-CM25</t>
+          <t>1725-5144-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,42 +2861,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2906,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11457.42</v>
+        <v>20039.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>591-7471-CM25</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,58 +2922,62 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1564746.61</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>652-204-CM25</t>
+          <t>2766-844-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,53 +2992,57 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1637401.65</v>
+        <v>11457.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>548874-229-CM25</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,53 +3057,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>14153.37</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1005498-216-CM25</t>
+          <t>652-204-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3122,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3132,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3162,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>25350.68</v>
+        <v>1637401.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>711841-515-CM25</t>
+          <t>548874-229-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3183,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3193,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3124,20 +3216,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>23542.74</v>
+        <v>14153.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1725-5365-CM25</t>
+          <t>1005498-216-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3248,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,43 +3258,47 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>25949.03</v>
+        <v>25350.68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>709603-152-CM25</t>
+          <t>711841-515-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3313,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3323,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.980.220-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,20 +3346,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>54154.4</v>
+        <v>23542.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>765-349-CM25</t>
+          <t>1725-5365-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3373,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3388,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3418,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10590.65</v>
+        <v>25949.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>606-368-CM25</t>
+          <t>709603-152-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3434,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3449,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,28 +3464,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>128858.47</v>
+        <v>54154.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>711841-549-CM25</t>
+          <t>765-349-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3504,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,17 +3514,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3429,20 +3537,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>16686.91</v>
+        <v>10590.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1398-2284-CM25</t>
+          <t>606-368-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,53 +3569,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>36105.67</v>
+        <v>128858.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4127-196-CM25</t>
+          <t>1398-2284-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,53 +3634,57 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>510212.77</v>
+        <v>36105.67</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>557639-1899-CM25</t>
+          <t>711841-549-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,58 +3694,62 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>56223.46</v>
+        <v>16686.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5153-2175-CM25</t>
+          <t>4127-196-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3759,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,28 +3789,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>28380.12</v>
+        <v>510212.77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5153-2195-CM25</t>
+          <t>557639-1899-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3829,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,27 +3839,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3869,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>68639.17</v>
+        <v>56223.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>45-349-CM25</t>
+          <t>5153-2175-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3890,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3915,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41671.09</v>
+        <v>28380.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>761-628-CM25</t>
+          <t>5153-2195-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,22 +3955,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,28 +3980,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>40057.03</v>
+        <v>68639.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>711841-600-CM25</t>
+          <t>45-349-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +4030,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3917,20 +4053,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>30902.16</v>
+        <v>41671.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2766-1078-CM25</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +4085,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,28 +4110,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7722.32</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2380-2242-CM25</t>
+          <t>711841-600-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,53 +4150,57 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>30283.05</v>
+        <v>30902.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1067455-173-CM25</t>
+          <t>2766-1078-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4215,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4225,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,28 +4240,32 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>66369.78999999999</v>
+        <v>7722.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>603663-378-CM25</t>
+          <t>2380-2242-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,53 +4280,57 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8783.790000000001</v>
+        <v>30283.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>584105-313-CM25</t>
+          <t>1067455-173-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4350,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,28 +4370,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>382106.17</v>
+        <v>66369.78999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>609-481-CM25</t>
+          <t>584105-313-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4410,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4420,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4435,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4450,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>31269.18</v>
+        <v>382106.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>765-409-CM25</t>
+          <t>603663-378-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4471,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,17 +4481,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4344,20 +4504,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>37572.09</v>
+        <v>8783.790000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1605-367-CM25</t>
+          <t>609-481-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4536,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4546,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,28 +4561,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>444468.14</v>
+        <v>31269.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>918434-450-CM25</t>
+          <t>765-409-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4596,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,17 +4611,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4466,20 +4634,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>171588.93</v>
+        <v>37572.09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1314-62-CM25</t>
+          <t>1605-367-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4661,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4691,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4706,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>20378.11</v>
+        <v>444468.14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>918434-450-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4727,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4737,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4588,20 +4760,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>32268.6</v>
+        <v>171588.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>1314-62-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4792,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,28 +4817,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>748610.75</v>
+        <v>20378.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1605-404-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4867,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4710,20 +4890,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>154680.16</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>519302-164-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4922,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4932,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.999.669-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4947,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4962,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>20674.73</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>1605-404-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4983,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,28 +5008,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>339530.09</v>
+        <v>154680.16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>1111089-522-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,27 +5048,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4900,13 +5088,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>339530.09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2777-884-CM25</t>
+          <t>519302-164-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,53 +5109,57 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>65.999.669-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>154690.6</v>
+        <v>20674.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2766-1316-CM25</t>
+          <t>1057414-768-SE25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,58 +5169,62 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7057.25</v>
+        <v>77508.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>876-352-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5234,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,27 +5249,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5279,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>68186.2</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3944-345-CM25</t>
+          <t>2777-884-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5295,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5340,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>50321.79</v>
+        <v>154690.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1005498-305-SE25</t>
+          <t>2766-1316-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5361,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5371,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5405,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>83686.95</v>
+        <v>7057.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>937232-1121-CM25</t>
+          <t>876-352-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,7 +5426,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5240,12 +5436,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,28 +5451,32 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>501384.71</v>
+        <v>68186.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>1195104-395-SE25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5291,7 +5491,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5301,12 +5501,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,28 +5516,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>626037.92</v>
+        <v>165235.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>635-5072-CM25</t>
+          <t>3944-345-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,7 +5556,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5362,17 +5566,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5392,13 +5596,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>34583.87</v>
+        <v>50321.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3232-795-CM25</t>
+          <t>1005498-305-SE25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5413,53 +5617,57 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>35024.99</v>
+        <v>83686.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>937232-1121-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,22 +5682,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5707,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5518,13 +5726,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>901825.33</v>
+        <v>501384.71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>1177296-473-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5539,7 +5747,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5549,12 +5757,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5564,12 +5772,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5579,13 +5787,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>68833.08</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>635-5072-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5595,12 +5803,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5610,27 +5818,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5640,13 +5848,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>291592.37</v>
+        <v>34583.87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>3232-795-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5656,12 +5864,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5671,43 +5879,47 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>48887.01</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2428-1-CM26</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5717,58 +5929,62 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>16696.03</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1233616-170-CM26</t>
+          <t>609-569-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5778,12 +5994,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5793,43 +6009,47 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>15074.98</v>
+        <v>68833.08</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5844,7 +6064,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5854,12 +6074,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5869,12 +6089,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5884,13 +6104,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>664434.1899999999</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>635-84-CM26</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5905,7 +6125,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5915,27 +6135,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5945,13 +6165,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>22477.75</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>612-49-SE26</t>
+          <t>2428-1-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5961,42 +6181,42 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6010,13 +6230,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>421786.91</v>
+        <v>16696.03</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2366-64-CM26</t>
+          <t>1233616-170-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6026,12 +6246,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6041,43 +6261,47 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>34277.51</v>
+        <v>15074.98</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2677-36-CM26</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6087,12 +6311,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6102,43 +6326,47 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>63261.21</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>711841-49-SE26</t>
+          <t>635-84-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6148,12 +6376,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6163,47 +6391,43 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>224012.71</v>
+        <v>22477.75</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>612-49-SE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6218,7 +6442,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6228,43 +6452,47 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>40809.78</v>
+        <v>421786.91</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>2366-64-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6279,7 +6507,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6289,27 +6517,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6319,13 +6547,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>48811.95</v>
+        <v>34277.51</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>2677-36-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6340,7 +6568,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6350,47 +6578,43 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7902.37</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>711841-49-SE26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6405,53 +6629,57 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>45592.37</v>
+        <v>224012.71</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5153-348-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6466,7 +6694,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6476,17 +6704,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6499,20 +6727,24 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>75841.3</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5153-349-CM26</t>
+          <t>1725-83-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6527,37 +6759,37 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6567,13 +6799,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>77108.33</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057501-2182-CM26</t>
+          <t>609-31-SE26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6588,22 +6820,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6613,28 +6845,32 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>16288.11</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1035206-191-CM25</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6644,12 +6880,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6659,12 +6895,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6674,12 +6910,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6689,13 +6925,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>185339.03</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>5153-349-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6705,12 +6941,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6720,43 +6956,47 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>47308.62</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>5153-348-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6766,12 +7006,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6781,43 +7021,47 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>15723.01</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>1057501-2182-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6827,58 +7071,62 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>750328.3100000001</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>545774-18-CM26</t>
+          <t>1035206-191-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6888,12 +7136,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6903,17 +7151,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6926,20 +7174,24 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>39248.25</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>1704-1373-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6949,12 +7201,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6964,27 +7216,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6994,13 +7246,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>681911.34</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>5416-143-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7010,12 +7262,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7025,27 +7277,27 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7055,13 +7307,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>46529.02</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7071,58 +7323,62 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>46529.02</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2766-212-CM26</t>
+          <t>545774-18-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7132,12 +7388,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7147,12 +7403,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7170,20 +7426,24 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7350.17</v>
+        <v>39248.25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1415862-28-SE26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7193,27 +7453,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7223,12 +7483,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7242,13 +7502,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>357020.86</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7263,27 +7523,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7303,13 +7563,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>316206.29</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5574-43-CM26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7324,7 +7584,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7334,27 +7594,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7364,13 +7624,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>57074.88</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>599-82-CM26</t>
+          <t>2766-212-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7385,22 +7645,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7410,28 +7670,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>71491.19</v>
+        <v>7350.17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2766-277-CM26</t>
+          <t>1415862-28-SE26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7446,22 +7710,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7471,28 +7735,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>14001.95</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7507,7 +7775,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7517,12 +7785,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7532,12 +7800,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7547,13 +7815,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>109632.69</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>5574-43-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7563,27 +7831,27 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7593,28 +7861,32 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>91015.17999999999</v>
+        <v>57074.88</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>2766-277-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7624,12 +7896,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7639,12 +7911,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7654,28 +7926,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1696277.88</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5586-761-CM26</t>
+          <t>599-82-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7685,58 +7961,62 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>133390.47</v>
+        <v>71491.19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>599-58-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7746,27 +8026,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7776,28 +8056,32 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>482098.69</v>
+        <v>109632.69</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>876-114-SE26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7807,58 +8091,62 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>913082.5600000001</v>
+        <v>178647.35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>869591-35-CM26</t>
+          <t>621923-26-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7868,27 +8156,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7898,12 +8186,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7913,13 +8201,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>50266.24</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>894244-4-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7934,7 +8222,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7944,27 +8232,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7974,13 +8262,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>15606.73</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2455-107-CM26</t>
+          <t>5586-761-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7995,7 +8283,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8005,17 +8293,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8028,20 +8316,24 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>260658.45</v>
+        <v>133390.47</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>606-299-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8056,7 +8348,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8066,12 +8358,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8081,12 +8373,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8096,13 +8388,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>135674.88</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>591-90-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8112,12 +8404,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8142,12 +8434,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8157,13 +8449,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1718926.68</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>711841-228-CM26</t>
+          <t>869591-35-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8173,12 +8465,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8188,12 +8480,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8203,28 +8495,32 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>18470.68</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1016-73-CM26</t>
+          <t>765-158-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8234,12 +8530,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8249,17 +8545,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8272,20 +8568,24 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>30606.2</v>
+        <v>15606.73</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>606-311-CM26</t>
+          <t>2455-107-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8295,27 +8595,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8325,28 +8625,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>85311.75</v>
+        <v>260658.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>622-302-CM26</t>
+          <t>606-299-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8356,12 +8660,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8371,12 +8675,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8394,20 +8698,24 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>24372.73</v>
+        <v>135674.88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2345-267-CM26</t>
+          <t>1057414-512-SE26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8422,7 +8730,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8432,43 +8740,47 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>330201.73</v>
+        <v>2956.49</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1005498-124-CM26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8483,53 +8795,57 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>60231.56</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1005498-132-CM26</t>
+          <t>711841-228-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8539,12 +8855,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8554,12 +8870,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8569,28 +8885,32 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>24744.2</v>
+        <v>18470.68</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>870-209-CM26</t>
+          <t>1016-73-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8600,27 +8920,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8630,28 +8950,32 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>177904.1</v>
+        <v>30606.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4931-114-CM26</t>
+          <t>606-311-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8661,27 +8985,27 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8691,28 +9015,32 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>274977.66</v>
+        <v>85311.75</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2766-572-CM26</t>
+          <t>622-302-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8722,12 +9050,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8737,12 +9065,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8752,28 +9080,32 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8351.34</v>
+        <v>24372.73</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5153-1605-CM26</t>
+          <t>2345-267-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8783,12 +9115,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8798,12 +9130,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8813,12 +9145,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8828,67 +9160,457 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>37202.6</v>
+        <v>330201.73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>1005498-124-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>60231.56</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1005498-132-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>24744.2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>870-209-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>60.718.000-8</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>COMISION NACIONAL DE RIEGO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>177904.1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4931-114-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>274977.66</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2766-572-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>69.072.000-0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>8351.34</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>5153-1605-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>37202.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>606-375-CM26</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>60.513.000-3</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
         <is>
           <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M138" s="2" t="n">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
         <v>12951.04</v>
       </c>
     </row>

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1001,7 +1005,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1062,7 +1070,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1587,7 +1599,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1635,20 +1647,24 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>138546.34</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>812261-1322-CM24</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1696,14 +1712,18 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>262605.26</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="21">
@@ -2395,7 +2415,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2456,7 +2480,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2899,7 +2927,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3411,7 +3443,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3619,7 +3655,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1398-2284-CM25</t>
+          <t>711841-549-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3639,32 +3675,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3678,13 +3714,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>36105.67</v>
+        <v>16686.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>711841-549-CM25</t>
+          <t>1398-2284-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3704,32 +3740,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3743,7 +3779,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>16686.91</v>
+        <v>36105.67</v>
       </c>
     </row>
     <row r="53">
@@ -4330,7 +4366,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1067455-173-CM25</t>
+          <t>603663-378-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4350,17 +4386,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4389,13 +4425,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>66369.78999999999</v>
+        <v>8783.790000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>584105-313-CM25</t>
+          <t>1067455-173-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4415,17 +4451,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4435,28 +4471,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>382106.17</v>
+        <v>66369.78999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>603663-378-CM25</t>
+          <t>584105-313-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4481,12 +4521,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4496,26 +4536,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8783.790000000001</v>
+        <v>382106.17</v>
       </c>
     </row>
     <row r="65">
@@ -5159,7 +5195,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057414-768-SE25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5184,47 +5220,43 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>77508.37</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>1057414-768-SE25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5249,37 +5281,41 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>77508.37</v>
       </c>
     </row>
     <row r="77">
@@ -5780,7 +5816,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6097,7 +6137,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6158,7 +6202,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +6840,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6805,7 +6857,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6825,32 +6877,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6864,13 +6916,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>7902.37</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>609-31-SE26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6890,42 +6942,46 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>45592.37</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="103">
@@ -7239,7 +7295,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7556,7 +7616,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7617,7 +7681,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7808,7 +7876,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +7893,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5574-43-CM26</t>
+          <t>2766-277-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7846,12 +7918,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7880,13 +7952,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>57074.88</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2766-277-CM26</t>
+          <t>5574-43-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7911,12 +7983,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7945,7 +8017,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>14001.95</v>
+        <v>57074.88</v>
       </c>
     </row>
     <row r="119">
@@ -8381,7 +8453,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8455,7 +8531,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>869591-35-CM26</t>
+          <t>765-158-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8480,27 +8556,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8514,13 +8590,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>50266.24</v>
+        <v>15606.73</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>765-158-CM26</t>
+          <t>869591-35-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8545,27 +8621,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8579,7 +8655,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>15606.73</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="129">
@@ -8715,7 +8791,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057414-512-SE26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8740,27 +8816,27 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8774,13 +8850,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2956.49</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>1057414-512-SE26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8805,27 +8881,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8839,7 +8915,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1718926.68</v>
+        <v>2956.49</v>
       </c>
     </row>
     <row r="133">
@@ -9612,6 +9688,197 @@
       </c>
       <c r="M144" s="2" t="n">
         <v>12951.04</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>599-190-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>43109.94</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1057414-652-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.607.300-1</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD BIO BIO</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>66920.25</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1216094-64-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>60966.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-proveedores/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -6495,7 +6495,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
